--- a/f4_disco_rtos/docs/APK6_Requirements_ASPICE_v1.1.xlsx
+++ b/f4_disco_rtos/docs/APK6_Requirements_ASPICE_v1.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUBEmx\rtos_opcode\f4_disco_rtos\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C1F706-3CEC-4DC4-8FA0-28FE0F640860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12C778D-15EE-4F84-997C-DAD5FD07456C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -2047,11 +2047,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2416,6 +2416,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{9CFE8C8C-9B1F-4F1A-A5F9-5BF429A3E9A7}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -2442,82 +2467,82 @@
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="24"/>
+      <c r="C4" s="25"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="25"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="25"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="25"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="24"/>
+      <c r="C8" s="25"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="25"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="24"/>
+      <c r="C10" s="25"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="25"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="25"/>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -3603,7 +3628,7 @@
       <c r="B14" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="23" t="s">
         <v>180</v>
       </c>
       <c r="D14" s="16" t="s">
